--- a/healthcare_forms/013_health_and_travel_history_declaration_form--healthcare_forms.xlsx
+++ b/healthcare_forms/013_health_and_travel_history_declaration_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Page 1</t>
+          <t>1. General Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>health_and_travel_history</t>
+          <t>health_status</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Health and Travel History</t>
+          <t>2. Current Health Status</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -558,53 +558,61 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>symptoms</t>
+          <t>countries_visited_recently</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Symptoms</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>3. Countries Visited in Last 2 Weeks</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>List all countries you have visited in the last 2 weeks.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>contacted_areas</t>
+          <t>reasons_for_visit</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Contacted Areas</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>4. Reasons for Visit</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>State the reasons for your visit.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -616,18 +624,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>countries_visited</t>
+          <t>symptoms</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Countries Visited</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>5. Symptoms</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>List all the symptoms you are experiencing.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -639,45 +651,49 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>countries_visited</t>
+          <t>countries_planned_visit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Countries Visited</t>
+          <t>6. Countries to Visit in Next 2 Weeks</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>List all countries you have visited in the last two weeks.</t>
+          <t>List all countries you plan to visit in the next 2 weeks.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>reasons_for_visit</t>
+          <t>contacted_areas</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>reasons-for-visit</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>7. Contacted Areas</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>List all areas you have contacted in the last 2 weeks.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -689,237 +705,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>reasons_for_visit</t>
+          <t>covid_contact</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reasons for Visit</t>
+          <t>8. Contact with COVID-19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>State the reasons for your visit.</t>
+          <t>Have you been in contact with anyone with COVID-19 in the last 2 weeks?</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>symptoms</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Symptoms</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>symptoms</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Symptoms</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>symptoms</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Symptoms</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>symptoms</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Symptoms</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>contacted_areas</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Contacted Areas</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>List all areas you have contacted.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>contacted_areas</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Contacted Areas</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>List areas you have contacted.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>countries_visited</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Countries Visited</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>reasons_for_visit</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Reasons for Visit</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>reasons_for_visit</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Reasons for Visit</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -934,11 +735,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -962,34 +763,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>countries_visited_choices</t>
+          <t>countries_visited_recently_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>countries_visited_choices</t>
+          <t>countries_visited_recently_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1001,12 +802,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1018,46 +819,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>contacted_areas_choices</t>
+          <t>countries_planned_visit_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>contacted_areas_choices</t>
+          <t>countries_planned_visit_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1069,12 +870,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1086,114 +887,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>countries_visited_choices</t>
+          <t>covid_contact_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>countries_visited_choices</t>
+          <t>covid_contact_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>reasons_for_visit_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>reasons_for_visit_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>reasons_for_visit_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>reasons_for_visit_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
